--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,60 +790,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133015828</v>
+        <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>57847</v>
+        <v>91472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100096</v>
+        <v>2008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sverkersholm, Ög</t>
+          <t>Bredviksudde, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578798</v>
+        <v>578801</v>
       </c>
       <c r="R3" t="n">
-        <v>6469537</v>
+        <v>6469450</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +899,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Lindgren, oskar österholm</t>
+          <t>William Rosén, oskar österholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133015828</t>
+          <t>https://artportalen.se/Sighting/136015351</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133016020</v>
+        <v>133015828</v>
       </c>
       <c r="B4" t="n">
-        <v>58461</v>
+        <v>57847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>100096</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,7 +953,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578762</v>
+        <v>578798</v>
       </c>
       <c r="R4" t="n">
-        <v>6469452</v>
+        <v>6469537</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,16 +1024,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133016020</t>
+          <t>https://artportalen.se/Sighting/133015828</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133016011</v>
+        <v>133016020</v>
       </c>
       <c r="B5" t="n">
-        <v>58658</v>
+        <v>58461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,7 +1067,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1065,7 +1077,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578767</v>
+        <v>578762</v>
       </c>
       <c r="R5" t="n">
         <v>6469452</v>
@@ -1126,16 +1138,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133016011</t>
+          <t>https://artportalen.se/Sighting/133016020</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133016002</v>
+        <v>133016011</v>
       </c>
       <c r="B6" t="n">
-        <v>58812</v>
+        <v>58658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,16 +1155,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1165,10 +1177,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578774</v>
+        <v>578767</v>
       </c>
       <c r="R6" t="n">
-        <v>6469455</v>
+        <v>6469452</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1235,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,16 +1252,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133016002</t>
+          <t>https://artportalen.se/Sighting/133016011</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133015990</v>
+        <v>133016002</v>
       </c>
       <c r="B7" t="n">
-        <v>99001</v>
+        <v>58812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,27 +1269,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223049</v>
+        <v>208245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578796</v>
+        <v>578774</v>
       </c>
       <c r="R7" t="n">
-        <v>6469477</v>
+        <v>6469455</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,16 +1364,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133015990</t>
+          <t>https://artportalen.se/Sighting/133016002</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131867043</v>
+        <v>133015990</v>
       </c>
       <c r="B8" t="n">
-        <v>84199</v>
+        <v>99001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,30 +1381,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>232272</v>
+        <v>223049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578799</v>
+        <v>578796</v>
       </c>
       <c r="R8" t="n">
-        <v>6469483</v>
+        <v>6469477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,12 +1439,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,6 +1470,116 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133015990</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131867043</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sverkersholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>578799</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6469483</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Valdemarsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ringarum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emil Lindgren, oskar österholm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131867043</t>
         </is>
@@ -1468,6 +1594,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91472</v>
+        <v>91474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91474</v>
+        <v>91475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91475</v>
+        <v>91476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91476</v>
+        <v>91477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91477</v>
+        <v>91483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91483</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91490</v>
+        <v>91497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91497</v>
+        <v>91498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91498</v>
+        <v>91511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91511</v>
+        <v>91512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
